--- a/bankole_2026/documentation/09_network_02lmm.xlsx
+++ b/bankole_2026/documentation/09_network_02lmm.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
   <si>
     <t xml:space="preserve">Project Name</t>
   </si>
@@ -310,17 +310,6 @@
   <si>
     <t xml:space="preserve">/Tables/all_componets_w_topology.csv</t>
   </si>
-  <si>
-    <t xml:space="preserve">make the counts for figure 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">count_for_flowchart_09lmm.sas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tables/comp_orgn_anno_xpr.csv
-comp_orgn_anno_xpr_byspecies.csv
-comp_anno_xpr.csv</t>
-  </si>
 </sst>
 </file>
 
@@ -329,7 +318,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -389,6 +378,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC9211E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -442,7 +439,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -477,6 +474,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -543,7 +548,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC9211E"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -663,7 +668,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:AMJ30"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -980,7 +985,7 @@
       <c r="D25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G25" s="0"/>
+      <c r="G25" s="7"/>
       <c r="H25" s="1" t="s">
         <v>62</v>
       </c>
@@ -1006,11 +1011,11 @@
       <c r="D27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="0"/>
+      <c r="E27" s="7"/>
       <c r="F27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G27" s="0"/>
+      <c r="G27" s="7"/>
       <c r="H27" s="1" t="s">
         <v>68</v>
       </c>
@@ -1029,19 +1034,1031 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>74</v>
-      </c>
+    <row r="30" s="10" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
+      <c r="AB30" s="9"/>
+      <c r="AC30" s="9"/>
+      <c r="AD30" s="9"/>
+      <c r="AE30" s="9"/>
+      <c r="AF30" s="9"/>
+      <c r="AG30" s="9"/>
+      <c r="AH30" s="9"/>
+      <c r="AI30" s="9"/>
+      <c r="AJ30" s="9"/>
+      <c r="AK30" s="9"/>
+      <c r="AL30" s="9"/>
+      <c r="AM30" s="9"/>
+      <c r="AN30" s="9"/>
+      <c r="AO30" s="9"/>
+      <c r="AP30" s="9"/>
+      <c r="AQ30" s="9"/>
+      <c r="AR30" s="9"/>
+      <c r="AS30" s="9"/>
+      <c r="AT30" s="9"/>
+      <c r="AU30" s="9"/>
+      <c r="AV30" s="9"/>
+      <c r="AW30" s="9"/>
+      <c r="AX30" s="9"/>
+      <c r="AY30" s="9"/>
+      <c r="AZ30" s="9"/>
+      <c r="BA30" s="9"/>
+      <c r="BB30" s="9"/>
+      <c r="BC30" s="9"/>
+      <c r="BD30" s="9"/>
+      <c r="BE30" s="9"/>
+      <c r="BF30" s="9"/>
+      <c r="BG30" s="9"/>
+      <c r="BH30" s="9"/>
+      <c r="BI30" s="9"/>
+      <c r="BJ30" s="9"/>
+      <c r="BK30" s="9"/>
+      <c r="BL30" s="9"/>
+      <c r="BM30" s="9"/>
+      <c r="BN30" s="9"/>
+      <c r="BO30" s="9"/>
+      <c r="BP30" s="9"/>
+      <c r="BQ30" s="9"/>
+      <c r="BR30" s="9"/>
+      <c r="BS30" s="9"/>
+      <c r="BT30" s="9"/>
+      <c r="BU30" s="9"/>
+      <c r="BV30" s="9"/>
+      <c r="BW30" s="9"/>
+      <c r="BX30" s="9"/>
+      <c r="BY30" s="9"/>
+      <c r="BZ30" s="9"/>
+      <c r="CA30" s="9"/>
+      <c r="CB30" s="9"/>
+      <c r="CC30" s="9"/>
+      <c r="CD30" s="9"/>
+      <c r="CE30" s="9"/>
+      <c r="CF30" s="9"/>
+      <c r="CG30" s="9"/>
+      <c r="CH30" s="9"/>
+      <c r="CI30" s="9"/>
+      <c r="CJ30" s="9"/>
+      <c r="CK30" s="9"/>
+      <c r="CL30" s="9"/>
+      <c r="CM30" s="9"/>
+      <c r="CN30" s="9"/>
+      <c r="CO30" s="9"/>
+      <c r="CP30" s="9"/>
+      <c r="CQ30" s="9"/>
+      <c r="CR30" s="9"/>
+      <c r="CS30" s="9"/>
+      <c r="CT30" s="9"/>
+      <c r="CU30" s="9"/>
+      <c r="CV30" s="9"/>
+      <c r="CW30" s="9"/>
+      <c r="CX30" s="9"/>
+      <c r="CY30" s="9"/>
+      <c r="CZ30" s="9"/>
+      <c r="DA30" s="9"/>
+      <c r="DB30" s="9"/>
+      <c r="DC30" s="9"/>
+      <c r="DD30" s="9"/>
+      <c r="DE30" s="9"/>
+      <c r="DF30" s="9"/>
+      <c r="DG30" s="9"/>
+      <c r="DH30" s="9"/>
+      <c r="DI30" s="9"/>
+      <c r="DJ30" s="9"/>
+      <c r="DK30" s="9"/>
+      <c r="DL30" s="9"/>
+      <c r="DM30" s="9"/>
+      <c r="DN30" s="9"/>
+      <c r="DO30" s="9"/>
+      <c r="DP30" s="9"/>
+      <c r="DQ30" s="9"/>
+      <c r="DR30" s="9"/>
+      <c r="DS30" s="9"/>
+      <c r="DT30" s="9"/>
+      <c r="DU30" s="9"/>
+      <c r="DV30" s="9"/>
+      <c r="DW30" s="9"/>
+      <c r="DX30" s="9"/>
+      <c r="DY30" s="9"/>
+      <c r="DZ30" s="9"/>
+      <c r="EA30" s="9"/>
+      <c r="EB30" s="9"/>
+      <c r="EC30" s="9"/>
+      <c r="ED30" s="9"/>
+      <c r="EE30" s="9"/>
+      <c r="EF30" s="9"/>
+      <c r="EG30" s="9"/>
+      <c r="EH30" s="9"/>
+      <c r="EI30" s="9"/>
+      <c r="EJ30" s="9"/>
+      <c r="EK30" s="9"/>
+      <c r="EL30" s="9"/>
+      <c r="EM30" s="9"/>
+      <c r="EN30" s="9"/>
+      <c r="EO30" s="9"/>
+      <c r="EP30" s="9"/>
+      <c r="EQ30" s="9"/>
+      <c r="ER30" s="9"/>
+      <c r="ES30" s="9"/>
+      <c r="ET30" s="9"/>
+      <c r="EU30" s="9"/>
+      <c r="EV30" s="9"/>
+      <c r="EW30" s="9"/>
+      <c r="EX30" s="9"/>
+      <c r="EY30" s="9"/>
+      <c r="EZ30" s="9"/>
+      <c r="FA30" s="9"/>
+      <c r="FB30" s="9"/>
+      <c r="FC30" s="9"/>
+      <c r="FD30" s="9"/>
+      <c r="FE30" s="9"/>
+      <c r="FF30" s="9"/>
+      <c r="FG30" s="9"/>
+      <c r="FH30" s="9"/>
+      <c r="FI30" s="9"/>
+      <c r="FJ30" s="9"/>
+      <c r="FK30" s="9"/>
+      <c r="FL30" s="9"/>
+      <c r="FM30" s="9"/>
+      <c r="FN30" s="9"/>
+      <c r="FO30" s="9"/>
+      <c r="FP30" s="9"/>
+      <c r="FQ30" s="9"/>
+      <c r="FR30" s="9"/>
+      <c r="FS30" s="9"/>
+      <c r="FT30" s="9"/>
+      <c r="FU30" s="9"/>
+      <c r="FV30" s="9"/>
+      <c r="FW30" s="9"/>
+      <c r="FX30" s="9"/>
+      <c r="FY30" s="9"/>
+      <c r="FZ30" s="9"/>
+      <c r="GA30" s="9"/>
+      <c r="GB30" s="9"/>
+      <c r="GC30" s="9"/>
+      <c r="GD30" s="9"/>
+      <c r="GE30" s="9"/>
+      <c r="GF30" s="9"/>
+      <c r="GG30" s="9"/>
+      <c r="GH30" s="9"/>
+      <c r="GI30" s="9"/>
+      <c r="GJ30" s="9"/>
+      <c r="GK30" s="9"/>
+      <c r="GL30" s="9"/>
+      <c r="GM30" s="9"/>
+      <c r="GN30" s="9"/>
+      <c r="GO30" s="9"/>
+      <c r="GP30" s="9"/>
+      <c r="GQ30" s="9"/>
+      <c r="GR30" s="9"/>
+      <c r="GS30" s="9"/>
+      <c r="GT30" s="9"/>
+      <c r="GU30" s="9"/>
+      <c r="GV30" s="9"/>
+      <c r="GW30" s="9"/>
+      <c r="GX30" s="9"/>
+      <c r="GY30" s="9"/>
+      <c r="GZ30" s="9"/>
+      <c r="HA30" s="9"/>
+      <c r="HB30" s="9"/>
+      <c r="HC30" s="9"/>
+      <c r="HD30" s="9"/>
+      <c r="HE30" s="9"/>
+      <c r="HF30" s="9"/>
+      <c r="HG30" s="9"/>
+      <c r="HH30" s="9"/>
+      <c r="HI30" s="9"/>
+      <c r="HJ30" s="9"/>
+      <c r="HK30" s="9"/>
+      <c r="HL30" s="9"/>
+      <c r="HM30" s="9"/>
+      <c r="HN30" s="9"/>
+      <c r="HO30" s="9"/>
+      <c r="HP30" s="9"/>
+      <c r="HQ30" s="9"/>
+      <c r="HR30" s="9"/>
+      <c r="HS30" s="9"/>
+      <c r="HT30" s="9"/>
+      <c r="HU30" s="9"/>
+      <c r="HV30" s="9"/>
+      <c r="HW30" s="9"/>
+      <c r="HX30" s="9"/>
+      <c r="HY30" s="9"/>
+      <c r="HZ30" s="9"/>
+      <c r="IA30" s="9"/>
+      <c r="IB30" s="9"/>
+      <c r="IC30" s="9"/>
+      <c r="ID30" s="9"/>
+      <c r="IE30" s="9"/>
+      <c r="IF30" s="9"/>
+      <c r="IG30" s="9"/>
+      <c r="IH30" s="9"/>
+      <c r="II30" s="9"/>
+      <c r="IJ30" s="9"/>
+      <c r="IK30" s="9"/>
+      <c r="IL30" s="9"/>
+      <c r="IM30" s="9"/>
+      <c r="IN30" s="9"/>
+      <c r="IO30" s="9"/>
+      <c r="IP30" s="9"/>
+      <c r="IQ30" s="9"/>
+      <c r="IR30" s="9"/>
+      <c r="IS30" s="9"/>
+      <c r="IT30" s="9"/>
+      <c r="IU30" s="9"/>
+      <c r="IV30" s="9"/>
+      <c r="IW30" s="9"/>
+      <c r="IX30" s="9"/>
+      <c r="IY30" s="9"/>
+      <c r="IZ30" s="9"/>
+      <c r="JA30" s="9"/>
+      <c r="JB30" s="9"/>
+      <c r="JC30" s="9"/>
+      <c r="JD30" s="9"/>
+      <c r="JE30" s="9"/>
+      <c r="JF30" s="9"/>
+      <c r="JG30" s="9"/>
+      <c r="JH30" s="9"/>
+      <c r="JI30" s="9"/>
+      <c r="JJ30" s="9"/>
+      <c r="JK30" s="9"/>
+      <c r="JL30" s="9"/>
+      <c r="JM30" s="9"/>
+      <c r="JN30" s="9"/>
+      <c r="JO30" s="9"/>
+      <c r="JP30" s="9"/>
+      <c r="JQ30" s="9"/>
+      <c r="JR30" s="9"/>
+      <c r="JS30" s="9"/>
+      <c r="JT30" s="9"/>
+      <c r="JU30" s="9"/>
+      <c r="JV30" s="9"/>
+      <c r="JW30" s="9"/>
+      <c r="JX30" s="9"/>
+      <c r="JY30" s="9"/>
+      <c r="JZ30" s="9"/>
+      <c r="KA30" s="9"/>
+      <c r="KB30" s="9"/>
+      <c r="KC30" s="9"/>
+      <c r="KD30" s="9"/>
+      <c r="KE30" s="9"/>
+      <c r="KF30" s="9"/>
+      <c r="KG30" s="9"/>
+      <c r="KH30" s="9"/>
+      <c r="KI30" s="9"/>
+      <c r="KJ30" s="9"/>
+      <c r="KK30" s="9"/>
+      <c r="KL30" s="9"/>
+      <c r="KM30" s="9"/>
+      <c r="KN30" s="9"/>
+      <c r="KO30" s="9"/>
+      <c r="KP30" s="9"/>
+      <c r="KQ30" s="9"/>
+      <c r="KR30" s="9"/>
+      <c r="KS30" s="9"/>
+      <c r="KT30" s="9"/>
+      <c r="KU30" s="9"/>
+      <c r="KV30" s="9"/>
+      <c r="KW30" s="9"/>
+      <c r="KX30" s="9"/>
+      <c r="KY30" s="9"/>
+      <c r="KZ30" s="9"/>
+      <c r="LA30" s="9"/>
+      <c r="LB30" s="9"/>
+      <c r="LC30" s="9"/>
+      <c r="LD30" s="9"/>
+      <c r="LE30" s="9"/>
+      <c r="LF30" s="9"/>
+      <c r="LG30" s="9"/>
+      <c r="LH30" s="9"/>
+      <c r="LI30" s="9"/>
+      <c r="LJ30" s="9"/>
+      <c r="LK30" s="9"/>
+      <c r="LL30" s="9"/>
+      <c r="LM30" s="9"/>
+      <c r="LN30" s="9"/>
+      <c r="LO30" s="9"/>
+      <c r="LP30" s="9"/>
+      <c r="LQ30" s="9"/>
+      <c r="LR30" s="9"/>
+      <c r="LS30" s="9"/>
+      <c r="LT30" s="9"/>
+      <c r="LU30" s="9"/>
+      <c r="LV30" s="9"/>
+      <c r="LW30" s="9"/>
+      <c r="LX30" s="9"/>
+      <c r="LY30" s="9"/>
+      <c r="LZ30" s="9"/>
+      <c r="MA30" s="9"/>
+      <c r="MB30" s="9"/>
+      <c r="MC30" s="9"/>
+      <c r="MD30" s="9"/>
+      <c r="ME30" s="9"/>
+      <c r="MF30" s="9"/>
+      <c r="MG30" s="9"/>
+      <c r="MH30" s="9"/>
+      <c r="MI30" s="9"/>
+      <c r="MJ30" s="9"/>
+      <c r="MK30" s="9"/>
+      <c r="ML30" s="9"/>
+      <c r="MM30" s="9"/>
+      <c r="MN30" s="9"/>
+      <c r="MO30" s="9"/>
+      <c r="MP30" s="9"/>
+      <c r="MQ30" s="9"/>
+      <c r="MR30" s="9"/>
+      <c r="MS30" s="9"/>
+      <c r="MT30" s="9"/>
+      <c r="MU30" s="9"/>
+      <c r="MV30" s="9"/>
+      <c r="MW30" s="9"/>
+      <c r="MX30" s="9"/>
+      <c r="MY30" s="9"/>
+      <c r="MZ30" s="9"/>
+      <c r="NA30" s="9"/>
+      <c r="NB30" s="9"/>
+      <c r="NC30" s="9"/>
+      <c r="ND30" s="9"/>
+      <c r="NE30" s="9"/>
+      <c r="NF30" s="9"/>
+      <c r="NG30" s="9"/>
+      <c r="NH30" s="9"/>
+      <c r="NI30" s="9"/>
+      <c r="NJ30" s="9"/>
+      <c r="NK30" s="9"/>
+      <c r="NL30" s="9"/>
+      <c r="NM30" s="9"/>
+      <c r="NN30" s="9"/>
+      <c r="NO30" s="9"/>
+      <c r="NP30" s="9"/>
+      <c r="NQ30" s="9"/>
+      <c r="NR30" s="9"/>
+      <c r="NS30" s="9"/>
+      <c r="NT30" s="9"/>
+      <c r="NU30" s="9"/>
+      <c r="NV30" s="9"/>
+      <c r="NW30" s="9"/>
+      <c r="NX30" s="9"/>
+      <c r="NY30" s="9"/>
+      <c r="NZ30" s="9"/>
+      <c r="OA30" s="9"/>
+      <c r="OB30" s="9"/>
+      <c r="OC30" s="9"/>
+      <c r="OD30" s="9"/>
+      <c r="OE30" s="9"/>
+      <c r="OF30" s="9"/>
+      <c r="OG30" s="9"/>
+      <c r="OH30" s="9"/>
+      <c r="OI30" s="9"/>
+      <c r="OJ30" s="9"/>
+      <c r="OK30" s="9"/>
+      <c r="OL30" s="9"/>
+      <c r="OM30" s="9"/>
+      <c r="ON30" s="9"/>
+      <c r="OO30" s="9"/>
+      <c r="OP30" s="9"/>
+      <c r="OQ30" s="9"/>
+      <c r="OR30" s="9"/>
+      <c r="OS30" s="9"/>
+      <c r="OT30" s="9"/>
+      <c r="OU30" s="9"/>
+      <c r="OV30" s="9"/>
+      <c r="OW30" s="9"/>
+      <c r="OX30" s="9"/>
+      <c r="OY30" s="9"/>
+      <c r="OZ30" s="9"/>
+      <c r="PA30" s="9"/>
+      <c r="PB30" s="9"/>
+      <c r="PC30" s="9"/>
+      <c r="PD30" s="9"/>
+      <c r="PE30" s="9"/>
+      <c r="PF30" s="9"/>
+      <c r="PG30" s="9"/>
+      <c r="PH30" s="9"/>
+      <c r="PI30" s="9"/>
+      <c r="PJ30" s="9"/>
+      <c r="PK30" s="9"/>
+      <c r="PL30" s="9"/>
+      <c r="PM30" s="9"/>
+      <c r="PN30" s="9"/>
+      <c r="PO30" s="9"/>
+      <c r="PP30" s="9"/>
+      <c r="PQ30" s="9"/>
+      <c r="PR30" s="9"/>
+      <c r="PS30" s="9"/>
+      <c r="PT30" s="9"/>
+      <c r="PU30" s="9"/>
+      <c r="PV30" s="9"/>
+      <c r="PW30" s="9"/>
+      <c r="PX30" s="9"/>
+      <c r="PY30" s="9"/>
+      <c r="PZ30" s="9"/>
+      <c r="QA30" s="9"/>
+      <c r="QB30" s="9"/>
+      <c r="QC30" s="9"/>
+      <c r="QD30" s="9"/>
+      <c r="QE30" s="9"/>
+      <c r="QF30" s="9"/>
+      <c r="QG30" s="9"/>
+      <c r="QH30" s="9"/>
+      <c r="QI30" s="9"/>
+      <c r="QJ30" s="9"/>
+      <c r="QK30" s="9"/>
+      <c r="QL30" s="9"/>
+      <c r="QM30" s="9"/>
+      <c r="QN30" s="9"/>
+      <c r="QO30" s="9"/>
+      <c r="QP30" s="9"/>
+      <c r="QQ30" s="9"/>
+      <c r="QR30" s="9"/>
+      <c r="QS30" s="9"/>
+      <c r="QT30" s="9"/>
+      <c r="QU30" s="9"/>
+      <c r="QV30" s="9"/>
+      <c r="QW30" s="9"/>
+      <c r="QX30" s="9"/>
+      <c r="QY30" s="9"/>
+      <c r="QZ30" s="9"/>
+      <c r="RA30" s="9"/>
+      <c r="RB30" s="9"/>
+      <c r="RC30" s="9"/>
+      <c r="RD30" s="9"/>
+      <c r="RE30" s="9"/>
+      <c r="RF30" s="9"/>
+      <c r="RG30" s="9"/>
+      <c r="RH30" s="9"/>
+      <c r="RI30" s="9"/>
+      <c r="RJ30" s="9"/>
+      <c r="RK30" s="9"/>
+      <c r="RL30" s="9"/>
+      <c r="RM30" s="9"/>
+      <c r="RN30" s="9"/>
+      <c r="RO30" s="9"/>
+      <c r="RP30" s="9"/>
+      <c r="RQ30" s="9"/>
+      <c r="RR30" s="9"/>
+      <c r="RS30" s="9"/>
+      <c r="RT30" s="9"/>
+      <c r="RU30" s="9"/>
+      <c r="RV30" s="9"/>
+      <c r="RW30" s="9"/>
+      <c r="RX30" s="9"/>
+      <c r="RY30" s="9"/>
+      <c r="RZ30" s="9"/>
+      <c r="SA30" s="9"/>
+      <c r="SB30" s="9"/>
+      <c r="SC30" s="9"/>
+      <c r="SD30" s="9"/>
+      <c r="SE30" s="9"/>
+      <c r="SF30" s="9"/>
+      <c r="SG30" s="9"/>
+      <c r="SH30" s="9"/>
+      <c r="SI30" s="9"/>
+      <c r="SJ30" s="9"/>
+      <c r="SK30" s="9"/>
+      <c r="SL30" s="9"/>
+      <c r="SM30" s="9"/>
+      <c r="SN30" s="9"/>
+      <c r="SO30" s="9"/>
+      <c r="SP30" s="9"/>
+      <c r="SQ30" s="9"/>
+      <c r="SR30" s="9"/>
+      <c r="SS30" s="9"/>
+      <c r="ST30" s="9"/>
+      <c r="SU30" s="9"/>
+      <c r="SV30" s="9"/>
+      <c r="SW30" s="9"/>
+      <c r="SX30" s="9"/>
+      <c r="SY30" s="9"/>
+      <c r="SZ30" s="9"/>
+      <c r="TA30" s="9"/>
+      <c r="TB30" s="9"/>
+      <c r="TC30" s="9"/>
+      <c r="TD30" s="9"/>
+      <c r="TE30" s="9"/>
+      <c r="TF30" s="9"/>
+      <c r="TG30" s="9"/>
+      <c r="TH30" s="9"/>
+      <c r="TI30" s="9"/>
+      <c r="TJ30" s="9"/>
+      <c r="TK30" s="9"/>
+      <c r="TL30" s="9"/>
+      <c r="TM30" s="9"/>
+      <c r="TN30" s="9"/>
+      <c r="TO30" s="9"/>
+      <c r="TP30" s="9"/>
+      <c r="TQ30" s="9"/>
+      <c r="TR30" s="9"/>
+      <c r="TS30" s="9"/>
+      <c r="TT30" s="9"/>
+      <c r="TU30" s="9"/>
+      <c r="TV30" s="9"/>
+      <c r="TW30" s="9"/>
+      <c r="TX30" s="9"/>
+      <c r="TY30" s="9"/>
+      <c r="TZ30" s="9"/>
+      <c r="UA30" s="9"/>
+      <c r="UB30" s="9"/>
+      <c r="UC30" s="9"/>
+      <c r="UD30" s="9"/>
+      <c r="UE30" s="9"/>
+      <c r="UF30" s="9"/>
+      <c r="UG30" s="9"/>
+      <c r="UH30" s="9"/>
+      <c r="UI30" s="9"/>
+      <c r="UJ30" s="9"/>
+      <c r="UK30" s="9"/>
+      <c r="UL30" s="9"/>
+      <c r="UM30" s="9"/>
+      <c r="UN30" s="9"/>
+      <c r="UO30" s="9"/>
+      <c r="UP30" s="9"/>
+      <c r="UQ30" s="9"/>
+      <c r="UR30" s="9"/>
+      <c r="US30" s="9"/>
+      <c r="UT30" s="9"/>
+      <c r="UU30" s="9"/>
+      <c r="UV30" s="9"/>
+      <c r="UW30" s="9"/>
+      <c r="UX30" s="9"/>
+      <c r="UY30" s="9"/>
+      <c r="UZ30" s="9"/>
+      <c r="VA30" s="9"/>
+      <c r="VB30" s="9"/>
+      <c r="VC30" s="9"/>
+      <c r="VD30" s="9"/>
+      <c r="VE30" s="9"/>
+      <c r="VF30" s="9"/>
+      <c r="VG30" s="9"/>
+      <c r="VH30" s="9"/>
+      <c r="VI30" s="9"/>
+      <c r="VJ30" s="9"/>
+      <c r="VK30" s="9"/>
+      <c r="VL30" s="9"/>
+      <c r="VM30" s="9"/>
+      <c r="VN30" s="9"/>
+      <c r="VO30" s="9"/>
+      <c r="VP30" s="9"/>
+      <c r="VQ30" s="9"/>
+      <c r="VR30" s="9"/>
+      <c r="VS30" s="9"/>
+      <c r="VT30" s="9"/>
+      <c r="VU30" s="9"/>
+      <c r="VV30" s="9"/>
+      <c r="VW30" s="9"/>
+      <c r="VX30" s="9"/>
+      <c r="VY30" s="9"/>
+      <c r="VZ30" s="9"/>
+      <c r="WA30" s="9"/>
+      <c r="WB30" s="9"/>
+      <c r="WC30" s="9"/>
+      <c r="WD30" s="9"/>
+      <c r="WE30" s="9"/>
+      <c r="WF30" s="9"/>
+      <c r="WG30" s="9"/>
+      <c r="WH30" s="9"/>
+      <c r="WI30" s="9"/>
+      <c r="WJ30" s="9"/>
+      <c r="WK30" s="9"/>
+      <c r="WL30" s="9"/>
+      <c r="WM30" s="9"/>
+      <c r="WN30" s="9"/>
+      <c r="WO30" s="9"/>
+      <c r="WP30" s="9"/>
+      <c r="WQ30" s="9"/>
+      <c r="WR30" s="9"/>
+      <c r="WS30" s="9"/>
+      <c r="WT30" s="9"/>
+      <c r="WU30" s="9"/>
+      <c r="WV30" s="9"/>
+      <c r="WW30" s="9"/>
+      <c r="WX30" s="9"/>
+      <c r="WY30" s="9"/>
+      <c r="WZ30" s="9"/>
+      <c r="XA30" s="9"/>
+      <c r="XB30" s="9"/>
+      <c r="XC30" s="9"/>
+      <c r="XD30" s="9"/>
+      <c r="XE30" s="9"/>
+      <c r="XF30" s="9"/>
+      <c r="XG30" s="9"/>
+      <c r="XH30" s="9"/>
+      <c r="XI30" s="9"/>
+      <c r="XJ30" s="9"/>
+      <c r="XK30" s="9"/>
+      <c r="XL30" s="9"/>
+      <c r="XM30" s="9"/>
+      <c r="XN30" s="9"/>
+      <c r="XO30" s="9"/>
+      <c r="XP30" s="9"/>
+      <c r="XQ30" s="9"/>
+      <c r="XR30" s="9"/>
+      <c r="XS30" s="9"/>
+      <c r="XT30" s="9"/>
+      <c r="XU30" s="9"/>
+      <c r="XV30" s="9"/>
+      <c r="XW30" s="9"/>
+      <c r="XX30" s="9"/>
+      <c r="XY30" s="9"/>
+      <c r="XZ30" s="9"/>
+      <c r="YA30" s="9"/>
+      <c r="YB30" s="9"/>
+      <c r="YC30" s="9"/>
+      <c r="YD30" s="9"/>
+      <c r="YE30" s="9"/>
+      <c r="YF30" s="9"/>
+      <c r="YG30" s="9"/>
+      <c r="YH30" s="9"/>
+      <c r="YI30" s="9"/>
+      <c r="YJ30" s="9"/>
+      <c r="YK30" s="9"/>
+      <c r="YL30" s="9"/>
+      <c r="YM30" s="9"/>
+      <c r="YN30" s="9"/>
+      <c r="YO30" s="9"/>
+      <c r="YP30" s="9"/>
+      <c r="YQ30" s="9"/>
+      <c r="YR30" s="9"/>
+      <c r="YS30" s="9"/>
+      <c r="YT30" s="9"/>
+      <c r="YU30" s="9"/>
+      <c r="YV30" s="9"/>
+      <c r="YW30" s="9"/>
+      <c r="YX30" s="9"/>
+      <c r="YY30" s="9"/>
+      <c r="YZ30" s="9"/>
+      <c r="ZA30" s="9"/>
+      <c r="ZB30" s="9"/>
+      <c r="ZC30" s="9"/>
+      <c r="ZD30" s="9"/>
+      <c r="ZE30" s="9"/>
+      <c r="ZF30" s="9"/>
+      <c r="ZG30" s="9"/>
+      <c r="ZH30" s="9"/>
+      <c r="ZI30" s="9"/>
+      <c r="ZJ30" s="9"/>
+      <c r="ZK30" s="9"/>
+      <c r="ZL30" s="9"/>
+      <c r="ZM30" s="9"/>
+      <c r="ZN30" s="9"/>
+      <c r="ZO30" s="9"/>
+      <c r="ZP30" s="9"/>
+      <c r="ZQ30" s="9"/>
+      <c r="ZR30" s="9"/>
+      <c r="ZS30" s="9"/>
+      <c r="ZT30" s="9"/>
+      <c r="ZU30" s="9"/>
+      <c r="ZV30" s="9"/>
+      <c r="ZW30" s="9"/>
+      <c r="ZX30" s="9"/>
+      <c r="ZY30" s="9"/>
+      <c r="ZZ30" s="9"/>
+      <c r="AAA30" s="9"/>
+      <c r="AAB30" s="9"/>
+      <c r="AAC30" s="9"/>
+      <c r="AAD30" s="9"/>
+      <c r="AAE30" s="9"/>
+      <c r="AAF30" s="9"/>
+      <c r="AAG30" s="9"/>
+      <c r="AAH30" s="9"/>
+      <c r="AAI30" s="9"/>
+      <c r="AAJ30" s="9"/>
+      <c r="AAK30" s="9"/>
+      <c r="AAL30" s="9"/>
+      <c r="AAM30" s="9"/>
+      <c r="AAN30" s="9"/>
+      <c r="AAO30" s="9"/>
+      <c r="AAP30" s="9"/>
+      <c r="AAQ30" s="9"/>
+      <c r="AAR30" s="9"/>
+      <c r="AAS30" s="9"/>
+      <c r="AAT30" s="9"/>
+      <c r="AAU30" s="9"/>
+      <c r="AAV30" s="9"/>
+      <c r="AAW30" s="9"/>
+      <c r="AAX30" s="9"/>
+      <c r="AAY30" s="9"/>
+      <c r="AAZ30" s="9"/>
+      <c r="ABA30" s="9"/>
+      <c r="ABB30" s="9"/>
+      <c r="ABC30" s="9"/>
+      <c r="ABD30" s="9"/>
+      <c r="ABE30" s="9"/>
+      <c r="ABF30" s="9"/>
+      <c r="ABG30" s="9"/>
+      <c r="ABH30" s="9"/>
+      <c r="ABI30" s="9"/>
+      <c r="ABJ30" s="9"/>
+      <c r="ABK30" s="9"/>
+      <c r="ABL30" s="9"/>
+      <c r="ABM30" s="9"/>
+      <c r="ABN30" s="9"/>
+      <c r="ABO30" s="9"/>
+      <c r="ABP30" s="9"/>
+      <c r="ABQ30" s="9"/>
+      <c r="ABR30" s="9"/>
+      <c r="ABS30" s="9"/>
+      <c r="ABT30" s="9"/>
+      <c r="ABU30" s="9"/>
+      <c r="ABV30" s="9"/>
+      <c r="ABW30" s="9"/>
+      <c r="ABX30" s="9"/>
+      <c r="ABY30" s="9"/>
+      <c r="ABZ30" s="9"/>
+      <c r="ACA30" s="9"/>
+      <c r="ACB30" s="9"/>
+      <c r="ACC30" s="9"/>
+      <c r="ACD30" s="9"/>
+      <c r="ACE30" s="9"/>
+      <c r="ACF30" s="9"/>
+      <c r="ACG30" s="9"/>
+      <c r="ACH30" s="9"/>
+      <c r="ACI30" s="9"/>
+      <c r="ACJ30" s="9"/>
+      <c r="ACK30" s="9"/>
+      <c r="ACL30" s="9"/>
+      <c r="ACM30" s="9"/>
+      <c r="ACN30" s="9"/>
+      <c r="ACO30" s="9"/>
+      <c r="ACP30" s="9"/>
+      <c r="ACQ30" s="9"/>
+      <c r="ACR30" s="9"/>
+      <c r="ACS30" s="9"/>
+      <c r="ACT30" s="9"/>
+      <c r="ACU30" s="9"/>
+      <c r="ACV30" s="9"/>
+      <c r="ACW30" s="9"/>
+      <c r="ACX30" s="9"/>
+      <c r="ACY30" s="9"/>
+      <c r="ACZ30" s="9"/>
+      <c r="ADA30" s="9"/>
+      <c r="ADB30" s="9"/>
+      <c r="ADC30" s="9"/>
+      <c r="ADD30" s="9"/>
+      <c r="ADE30" s="9"/>
+      <c r="ADF30" s="9"/>
+      <c r="ADG30" s="9"/>
+      <c r="ADH30" s="9"/>
+      <c r="ADI30" s="9"/>
+      <c r="ADJ30" s="9"/>
+      <c r="ADK30" s="9"/>
+      <c r="ADL30" s="9"/>
+      <c r="ADM30" s="9"/>
+      <c r="ADN30" s="9"/>
+      <c r="ADO30" s="9"/>
+      <c r="ADP30" s="9"/>
+      <c r="ADQ30" s="9"/>
+      <c r="ADR30" s="9"/>
+      <c r="ADS30" s="9"/>
+      <c r="ADT30" s="9"/>
+      <c r="ADU30" s="9"/>
+      <c r="ADV30" s="9"/>
+      <c r="ADW30" s="9"/>
+      <c r="ADX30" s="9"/>
+      <c r="ADY30" s="9"/>
+      <c r="ADZ30" s="9"/>
+      <c r="AEA30" s="9"/>
+      <c r="AEB30" s="9"/>
+      <c r="AEC30" s="9"/>
+      <c r="AED30" s="9"/>
+      <c r="AEE30" s="9"/>
+      <c r="AEF30" s="9"/>
+      <c r="AEG30" s="9"/>
+      <c r="AEH30" s="9"/>
+      <c r="AEI30" s="9"/>
+      <c r="AEJ30" s="9"/>
+      <c r="AEK30" s="9"/>
+      <c r="AEL30" s="9"/>
+      <c r="AEM30" s="9"/>
+      <c r="AEN30" s="9"/>
+      <c r="AEO30" s="9"/>
+      <c r="AEP30" s="9"/>
+      <c r="AEQ30" s="9"/>
+      <c r="AER30" s="9"/>
+      <c r="AES30" s="9"/>
+      <c r="AET30" s="9"/>
+      <c r="AEU30" s="9"/>
+      <c r="AEV30" s="9"/>
+      <c r="AEW30" s="9"/>
+      <c r="AEX30" s="9"/>
+      <c r="AEY30" s="9"/>
+      <c r="AEZ30" s="9"/>
+      <c r="AFA30" s="9"/>
+      <c r="AFB30" s="9"/>
+      <c r="AFC30" s="9"/>
+      <c r="AFD30" s="9"/>
+      <c r="AFE30" s="9"/>
+      <c r="AFF30" s="9"/>
+      <c r="AFG30" s="9"/>
+      <c r="AFH30" s="9"/>
+      <c r="AFI30" s="9"/>
+      <c r="AFJ30" s="9"/>
+      <c r="AFK30" s="9"/>
+      <c r="AFL30" s="9"/>
+      <c r="AFM30" s="9"/>
+      <c r="AFN30" s="9"/>
+      <c r="AFO30" s="9"/>
+      <c r="AFP30" s="9"/>
+      <c r="AFQ30" s="9"/>
+      <c r="AFR30" s="9"/>
+      <c r="AFS30" s="9"/>
+      <c r="AFT30" s="9"/>
+      <c r="AFU30" s="9"/>
+      <c r="AFV30" s="9"/>
+      <c r="AFW30" s="9"/>
+      <c r="AFX30" s="9"/>
+      <c r="AFY30" s="9"/>
+      <c r="AFZ30" s="9"/>
+      <c r="AGA30" s="9"/>
+      <c r="AGB30" s="9"/>
+      <c r="AGC30" s="9"/>
+      <c r="AGD30" s="9"/>
+      <c r="AGE30" s="9"/>
+      <c r="AGF30" s="9"/>
+      <c r="AGG30" s="9"/>
+      <c r="AGH30" s="9"/>
+      <c r="AGI30" s="9"/>
+      <c r="AGJ30" s="9"/>
+      <c r="AGK30" s="9"/>
+      <c r="AGL30" s="9"/>
+      <c r="AGM30" s="9"/>
+      <c r="AGN30" s="9"/>
+      <c r="AGO30" s="9"/>
+      <c r="AGP30" s="9"/>
+      <c r="AGQ30" s="9"/>
+      <c r="AGR30" s="9"/>
+      <c r="AGS30" s="9"/>
+      <c r="AGT30" s="9"/>
+      <c r="AGU30" s="9"/>
+      <c r="AGV30" s="9"/>
+      <c r="AGW30" s="9"/>
+      <c r="AGX30" s="9"/>
+      <c r="AGY30" s="9"/>
+      <c r="AGZ30" s="9"/>
+      <c r="AHA30" s="9"/>
+      <c r="AHB30" s="9"/>
+      <c r="AHC30" s="9"/>
+      <c r="AHD30" s="9"/>
+      <c r="AHE30" s="9"/>
+      <c r="AHF30" s="9"/>
+      <c r="AHG30" s="9"/>
+      <c r="AHH30" s="9"/>
+      <c r="AHI30" s="9"/>
+      <c r="AHJ30" s="9"/>
+      <c r="AHK30" s="9"/>
+      <c r="AHL30" s="9"/>
+      <c r="AHM30" s="9"/>
+      <c r="AHN30" s="9"/>
+      <c r="AHO30" s="9"/>
+      <c r="AHP30" s="9"/>
+      <c r="AHQ30" s="9"/>
+      <c r="AHR30" s="9"/>
+      <c r="AHS30" s="9"/>
+      <c r="AHT30" s="9"/>
+      <c r="AHU30" s="9"/>
+      <c r="AHV30" s="9"/>
+      <c r="AHW30" s="9"/>
+      <c r="AHX30" s="9"/>
+      <c r="AHY30" s="9"/>
+      <c r="AHZ30" s="9"/>
+      <c r="AIA30" s="9"/>
+      <c r="AIB30" s="9"/>
+      <c r="AIC30" s="9"/>
+      <c r="AID30" s="9"/>
+      <c r="AIE30" s="9"/>
+      <c r="AIF30" s="9"/>
+      <c r="AIG30" s="9"/>
+      <c r="AIH30" s="9"/>
+      <c r="AII30" s="9"/>
+      <c r="AIJ30" s="9"/>
+      <c r="AIK30" s="9"/>
+      <c r="AIL30" s="9"/>
+      <c r="AIM30" s="9"/>
+      <c r="AIN30" s="9"/>
+      <c r="AIO30" s="9"/>
+      <c r="AIP30" s="9"/>
+      <c r="AIQ30" s="9"/>
+      <c r="AIR30" s="9"/>
+      <c r="AIS30" s="9"/>
+      <c r="AIT30" s="9"/>
+      <c r="AIU30" s="9"/>
+      <c r="AIV30" s="9"/>
+      <c r="AIW30" s="9"/>
+      <c r="AIX30" s="9"/>
+      <c r="AIY30" s="9"/>
+      <c r="AIZ30" s="9"/>
+      <c r="AJA30" s="9"/>
+      <c r="AJB30" s="9"/>
+      <c r="AJC30" s="9"/>
+      <c r="AJD30" s="9"/>
+      <c r="AJE30" s="9"/>
+      <c r="AJF30" s="9"/>
+      <c r="AJG30" s="9"/>
+      <c r="AJH30" s="9"/>
+      <c r="AJI30" s="9"/>
+      <c r="AJJ30" s="9"/>
+      <c r="AJK30" s="9"/>
+      <c r="AJL30" s="9"/>
+      <c r="AJM30" s="9"/>
+      <c r="AJN30" s="9"/>
+      <c r="AJO30" s="9"/>
+      <c r="AJP30" s="9"/>
+      <c r="AJQ30" s="9"/>
+      <c r="AJR30" s="9"/>
+      <c r="AJS30" s="9"/>
+      <c r="AJT30" s="9"/>
+      <c r="AJU30" s="9"/>
+      <c r="AJV30" s="9"/>
+      <c r="AJW30" s="9"/>
+      <c r="AJX30" s="9"/>
+      <c r="AJY30" s="9"/>
+      <c r="AJZ30" s="9"/>
+      <c r="AKA30" s="9"/>
+      <c r="AKB30" s="9"/>
+      <c r="AKC30" s="9"/>
+      <c r="AKD30" s="9"/>
+      <c r="AKE30" s="9"/>
+      <c r="AKF30" s="9"/>
+      <c r="AKG30" s="9"/>
+      <c r="AKH30" s="9"/>
+      <c r="AKI30" s="9"/>
+      <c r="AKJ30" s="9"/>
+      <c r="AKK30" s="9"/>
+      <c r="AKL30" s="9"/>
+      <c r="AKM30" s="9"/>
+      <c r="AKN30" s="9"/>
+      <c r="AKO30" s="9"/>
+      <c r="AKP30" s="9"/>
+      <c r="AKQ30" s="9"/>
+      <c r="AKR30" s="9"/>
+      <c r="AKS30" s="9"/>
+      <c r="AKT30" s="9"/>
+      <c r="AKU30" s="9"/>
+      <c r="AKV30" s="9"/>
+      <c r="AKW30" s="9"/>
+      <c r="AKX30" s="9"/>
+      <c r="AKY30" s="9"/>
+      <c r="AKZ30" s="9"/>
+      <c r="ALA30" s="9"/>
+      <c r="ALB30" s="9"/>
+      <c r="ALC30" s="9"/>
+      <c r="ALD30" s="9"/>
+      <c r="ALE30" s="9"/>
+      <c r="ALF30" s="9"/>
+      <c r="ALG30" s="9"/>
+      <c r="ALH30" s="9"/>
+      <c r="ALI30" s="9"/>
+      <c r="ALJ30" s="9"/>
+      <c r="ALK30" s="9"/>
+      <c r="ALL30" s="9"/>
+      <c r="ALM30" s="9"/>
+      <c r="ALN30" s="9"/>
+      <c r="ALO30" s="9"/>
+      <c r="ALP30" s="9"/>
+      <c r="ALQ30" s="9"/>
+      <c r="ALR30" s="9"/>
+      <c r="ALS30" s="9"/>
+      <c r="ALT30" s="9"/>
+      <c r="ALU30" s="9"/>
+      <c r="ALV30" s="9"/>
+      <c r="ALW30" s="9"/>
+      <c r="ALX30" s="9"/>
+      <c r="ALY30" s="9"/>
+      <c r="ALZ30" s="9"/>
+      <c r="AMA30" s="9"/>
+      <c r="AMB30" s="9"/>
+      <c r="AMC30" s="9"/>
+      <c r="AMD30" s="9"/>
+      <c r="AME30" s="9"/>
+      <c r="AMF30" s="9"/>
+      <c r="AMG30" s="9"/>
+      <c r="AMH30" s="9"/>
+      <c r="AMI30" s="9"/>
+      <c r="AMJ30" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
